--- a/results/pr_AstroSync/exp/23MM/cv_scores/fair_cv_summary.xlsx
+++ b/results/pr_AstroSync/exp/23MM/cv_scores/fair_cv_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,12 +511,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -541,13 +541,13 @@
         <v>0.9444444444444445</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04593729597160074</v>
+        <v>0.03732064481335299</v>
       </c>
       <c r="O2" t="n">
-        <v>1.00284648930471</v>
+        <v>0.3779297614311366</v>
       </c>
     </row>
     <row r="3">
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -598,13 +598,13 @@
         <v>0.9444444444444445</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04648654808466881</v>
+        <v>0.04593729597160074</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9559366371305978</v>
+        <v>1.00284648930471</v>
       </c>
     </row>
     <row r="4">
@@ -630,38 +630,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05773502691896253</v>
+        <v>0.05773502691896255</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04614687813220873</v>
+        <v>0.04648654808466881</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9961331095464701</v>
+        <v>0.9559366371305978</v>
       </c>
     </row>
     <row r="5">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -703,22 +703,22 @@
         <v>0.9333333333333332</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9326599326599326</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9444444444444445</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05166306394962183</v>
+        <v>0.04614687813220873</v>
       </c>
       <c r="O5" t="n">
-        <v>0.442063394998617</v>
+        <v>0.9961331095464701</v>
       </c>
     </row>
     <row r="6">
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -760,22 +760,22 @@
         <v>0.9333333333333332</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06063724816350926</v>
+        <v>0.05166306394962183</v>
       </c>
       <c r="O6" t="n">
-        <v>0.193885880460579</v>
+        <v>0.442063394998617</v>
       </c>
     </row>
     <row r="7">
@@ -796,7 +796,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,7 +811,7 @@
         <v>0.9333333333333332</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.05773502691896253</v>
       </c>
       <c r="I7" t="n">
         <v>0.9333333333333332</v>
@@ -829,10 +829,10 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06474129366529535</v>
+        <v>0.06063724816350926</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2104409497010445</v>
+        <v>0.193885880460579</v>
       </c>
     </row>
     <row r="8">
@@ -858,7 +858,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -868,28 +868,28 @@
         <v>0.9333333333333332</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05773502691896253</v>
+        <v>0.1154700538379251</v>
       </c>
       <c r="I8" t="n">
         <v>0.9333333333333332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9326599326599326</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9444444444444445</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07001287352703149</v>
+        <v>0.06443160069466321</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2225274057522913</v>
+        <v>0.2233038649737258</v>
       </c>
     </row>
     <row r="9">
@@ -910,12 +910,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -931,22 +931,22 @@
         <v>0.9333333333333332</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9326599326599326</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9444444444444445</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9733333333333333</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07740456842092218</v>
+        <v>0.06474129366529535</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5297999884412222</v>
+        <v>0.2104409497010445</v>
       </c>
     </row>
     <row r="10">
@@ -967,43 +967,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.05773502691896253</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8956228956228957</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L10" t="n">
         <v>0.9444444444444445</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.96</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05598349479029877</v>
+        <v>0.07001287352703149</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3840111456129251</v>
+        <v>0.2225274057522913</v>
       </c>
     </row>
     <row r="11">
@@ -1024,43 +1024,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N11" t="n">
-        <v>0.05963869773457958</v>
+        <v>0.07740456842092218</v>
       </c>
       <c r="O11" t="n">
-        <v>0.979698193553288</v>
+        <v>0.5297999884412222</v>
       </c>
     </row>
     <row r="12">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1114,10 +1114,10 @@
         <v>0.9733333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06796373696407408</v>
+        <v>0.05598349479029877</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5166162541637292</v>
+        <v>0.3840111456129251</v>
       </c>
     </row>
     <row r="13">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1153,28 +1153,28 @@
         <v>0.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8962962962962964</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07350798110778552</v>
+        <v>0.05963869773457958</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2008389660512238</v>
+        <v>0.979698193553288</v>
       </c>
     </row>
     <row r="14">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1228,10 +1228,10 @@
         <v>0.9733333333333333</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08409597902878817</v>
+        <v>0.06796373696407408</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2741242496175685</v>
+        <v>0.5166162541637292</v>
       </c>
     </row>
     <row r="15">
@@ -1252,43 +1252,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8962962962962964</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.1527525231651947</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8518518518518517</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7999999999999999</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="M15" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09994137247881625</v>
+        <v>0.07350798110778552</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3087685673669738</v>
+        <v>0.2008389660512238</v>
       </c>
     </row>
     <row r="16">
@@ -1309,43 +1309,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8956228956228957</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.1527525231651947</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.8518518518518517</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.7999999999999999</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M16" t="n">
         <v>0.9733333333333333</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1010883752568569</v>
+        <v>0.08409597902878817</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3347212025408687</v>
+        <v>0.2741242496175685</v>
       </c>
     </row>
     <row r="17">
@@ -1366,43 +1366,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0577350269189626</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8585858585858586</v>
+        <v>0.9023569023569022</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L17" t="n">
-        <v>0.753968253968254</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="M17" t="n">
         <v>0.9866666666666667</v>
       </c>
       <c r="N17" t="n">
-        <v>0.105701449924948</v>
+        <v>0.08724616065109932</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3240243452148775</v>
+        <v>0.4579719108370012</v>
       </c>
     </row>
     <row r="18">
@@ -1428,38 +1428,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1154700538379252</v>
+        <v>0.05773502691896258</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.865993265993266</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1187183423272101</v>
+        <v>0.09686362255551799</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9507485036145545</v>
+        <v>0.3231923100519883</v>
       </c>
     </row>
     <row r="19">
@@ -1480,43 +1480,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1154700538379252</v>
+        <v>0.1527525231651947</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7898027898027897</v>
+        <v>0.8518518518518517</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9444444444444445</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9466666666666668</v>
+        <v>0.96</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1829357207114759</v>
+        <v>0.09994137247881625</v>
       </c>
       <c r="O19" t="n">
-        <v>1.545563642911307</v>
+        <v>0.3087685673669738</v>
       </c>
     </row>
     <row r="20">
@@ -1542,38 +1542,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1527525231651947</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8518518518518517</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.7999999999999999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1732050807568878</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.7999999999999999</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.746031746031746</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.6666666666666666</v>
       </c>
       <c r="L20" t="n">
         <v>0.9166666666666666</v>
       </c>
       <c r="M20" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N20" t="n">
-        <v>0.14874267187785</v>
+        <v>0.1010883752568569</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7742238119083592</v>
+        <v>0.3347212025408687</v>
       </c>
     </row>
     <row r="21">
@@ -1594,43 +1594,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1154700538379251</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.7999999999999999</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.7999999999999999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.8372183372183373</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.7242063492063492</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1702838037736091</v>
+        <v>0.114973997982046</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7872657721426127</v>
+        <v>1.821809484637733</v>
       </c>
     </row>
     <row r="22">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1656,38 +1656,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H22" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.0577350269189626</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9326599326599326</v>
+        <v>0.8585858585858586</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9444444444444445</v>
+        <v>0.753968253968254</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0536183287469908</v>
+        <v>0.105701449924948</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2104816867425708</v>
+        <v>0.3240243452148775</v>
       </c>
     </row>
     <row r="23">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1708,43 +1708,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.1154700538379252</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9326599326599326</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9444444444444445</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="M23" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N23" t="n">
-        <v>0.05936848011250212</v>
+        <v>0.1187183423272101</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2340885918826383</v>
+        <v>0.9507485036145545</v>
       </c>
     </row>
     <row r="24">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1765,43 +1765,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H24" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.1154700538379252</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9326599326599326</v>
+        <v>0.8624708624708625</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9444444444444445</v>
+        <v>0.763888888888889</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="N24" t="n">
-        <v>0.06247946108517414</v>
+        <v>0.1223189019184358</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2119377110309603</v>
+        <v>1.271776124475703</v>
       </c>
     </row>
     <row r="25">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1822,43 +1822,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09999999999999995</v>
+        <v>0.1527525231651947</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8962962962962964</v>
+        <v>0.8055555555555555</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N25" t="n">
-        <v>0.05438081979988104</v>
+        <v>0.1407820601183366</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1694847585189147</v>
+        <v>1.967255918337943</v>
       </c>
     </row>
     <row r="26">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1884,38 +1884,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09999999999999995</v>
+        <v>0.1154700538379252</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8962962962962964</v>
+        <v>0.7898027898027897</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.9466666666666668</v>
       </c>
       <c r="N26" t="n">
-        <v>0.07482893327090336</v>
+        <v>0.1829357207114759</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2213805630848505</v>
+        <v>1.545563642911307</v>
       </c>
     </row>
     <row r="27">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1941,38 +1941,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>0.1732050807568878</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.96</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0786727527471905</v>
+        <v>0.14874267187785</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2607063181008236</v>
+        <v>0.7742238119083592</v>
       </c>
     </row>
     <row r="28">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1993,43 +1993,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09999999999999995</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8962962962962964</v>
+        <v>0.8372183372183373</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.7242063492063492</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0803867152216408</v>
+        <v>0.1702838037736091</v>
       </c>
       <c r="O28" t="n">
-        <v>0.2348020570182513</v>
+        <v>0.7872657721426127</v>
       </c>
     </row>
     <row r="29">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2050,43 +2050,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>0.05773502691896253</v>
+        <v>0.2309401076758504</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8592592592592592</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8000000000000002</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="N29" t="n">
-        <v>0.06407046011051086</v>
+        <v>0.2032065733373818</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1866067120969328</v>
+        <v>2.601526294995471</v>
       </c>
     </row>
     <row r="30">
@@ -2107,43 +2107,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05773502691896253</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8592592592592592</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L30" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N30" t="n">
-        <v>0.08413828826308649</v>
+        <v>0.04919350371099241</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2445943862130808</v>
+        <v>0.2128886183890218</v>
       </c>
     </row>
     <row r="31">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2176,31 +2176,31 @@
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1154700538379251</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J31" t="n">
-        <v>0.85</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L31" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M31" t="n">
         <v>0.9733333333333333</v>
       </c>
       <c r="N31" t="n">
-        <v>0.08467875373428996</v>
+        <v>0.0536183287469908</v>
       </c>
       <c r="O31" t="n">
-        <v>0.257692886053034</v>
+        <v>0.2104816867425708</v>
       </c>
     </row>
     <row r="32">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2233,31 +2233,31 @@
         <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1527525231651947</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8518518518518517</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9733333333333333</v>
+        <v>0.96</v>
       </c>
       <c r="N32" t="n">
-        <v>0.09959105383177967</v>
+        <v>0.05936848011250212</v>
       </c>
       <c r="O32" t="n">
-        <v>0.4909658111702097</v>
+        <v>0.2340885918826383</v>
       </c>
     </row>
     <row r="33">
@@ -2278,43 +2278,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1527525231651947</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8222222222222223</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L33" t="n">
-        <v>0.85</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N33" t="n">
-        <v>0.09541183517697839</v>
+        <v>0.06247946108517414</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2984953852458652</v>
+        <v>0.2119377110309603</v>
       </c>
     </row>
     <row r="34">
@@ -2340,26 +2340,26 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.09999999999999995</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
-        <v>0.812962962962963</v>
+        <v>0.8962962962962964</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L34" t="n">
         <v>0.9333333333333332</v>
@@ -2368,10 +2368,10 @@
         <v>0.9866666666666667</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1140024409741974</v>
+        <v>0.05438081979988104</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3399214286171091</v>
+        <v>0.1694847585189147</v>
       </c>
     </row>
     <row r="35">
@@ -2392,43 +2392,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05773502691896256</v>
+        <v>0.09999999999999995</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8407407407407407</v>
+        <v>0.8962962962962964</v>
       </c>
       <c r="K35" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="L35" t="n">
-        <v>0.8380952380952381</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1323511061306422</v>
+        <v>0.07482893327090336</v>
       </c>
       <c r="O35" t="n">
-        <v>0.5161385881719551</v>
+        <v>0.2213805630848505</v>
       </c>
     </row>
     <row r="36">
@@ -2449,43 +2449,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1154700538379252</v>
+        <v>0.1732050807568878</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L36" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="M36" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1564311902153391</v>
+        <v>0.0786727527471905</v>
       </c>
       <c r="O36" t="n">
-        <v>0.5775214501620428</v>
+        <v>0.2607063181008236</v>
       </c>
     </row>
     <row r="37">
@@ -2506,43 +2506,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2</v>
+        <v>0.09999999999999995</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8055555555555555</v>
+        <v>0.8962962962962964</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="M37" t="n">
-        <v>0.88</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1261589706696185</v>
+        <v>0.0803867152216408</v>
       </c>
       <c r="O37" t="n">
-        <v>0.3777493300025176</v>
+        <v>0.2348020570182513</v>
       </c>
     </row>
     <row r="38">
@@ -2563,43 +2563,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2</v>
+        <v>0.09999999999999995</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.9074074074074074</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="N38" t="n">
-        <v>0.169359350595721</v>
+        <v>0.1040967880942367</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9743096114930762</v>
+        <v>0.9704863269935409</v>
       </c>
     </row>
     <row r="39">
@@ -2620,43 +2620,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2</v>
+        <v>0.05773502691896253</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.8592592592592592</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="L39" t="n">
         <v>0.9333333333333332</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1724033633384699</v>
+        <v>0.06407046011051086</v>
       </c>
       <c r="O39" t="n">
-        <v>1.070772041259389</v>
+        <v>0.1866067120969328</v>
       </c>
     </row>
     <row r="40">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2689,31 +2689,31 @@
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2516611478423583</v>
+        <v>0.05773502691896253</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.8592592592592592</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8933333333333334</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N40" t="n">
-        <v>0.199549230269577</v>
+        <v>0.08413828826308649</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8856247388141126</v>
+        <v>0.2445943862130808</v>
       </c>
     </row>
     <row r="41">
@@ -2734,42 +2734,954 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1154700538379251</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9733333333333333</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.08467875373428996</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.257692886053034</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1527525231651947</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8518518518518517</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9733333333333333</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.09959105383177967</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.4909658111702097</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1527525231651947</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8518518518518517</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9733333333333333</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.1022059031072373</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.5490052970391256</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.05773502691896253</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.1061630575225653</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.9658748868338521</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1527525231651947</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.872053872053872</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.1238343635266792</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5617579479500849</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1527525231651947</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.8222222222222223</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.09541183517697839</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.2984953852458652</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.05773502691896256</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.812962962962963</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.9866666666666667</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.1140024409741974</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.3399214286171091</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.05773502691896256</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8407407407407407</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.8380952380952381</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.9066666666666667</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.1323511061306422</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.5161385881719551</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>[8, 15]</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2081665999466133</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8296296296296296</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.1391307613146298</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.8050392139267112</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.2081665999466133</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.8518518518518517</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.8933333333333332</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.1508983118803316</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.8464319751316579</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2081665999466133</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.8518518518518517</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.1519325430566521</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.705227102497468</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>(0, 1, -2, -1)</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1154700538379252</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.1564311902153391</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.5775214501620428</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.8055555555555555</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.1261589706696185</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.3777493300025176</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.169359350595721</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.9743096114930762</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.1724033633384699</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.070772041259389</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.2516611478423583</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.8933333333333334</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.199549230269577</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8856247388141126</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>23MM</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
         <v>0.6333333333333333</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H57" t="n">
         <v>0.4041451884327381</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I57" t="n">
         <v>0.6333333333333333</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J57" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K57" t="n">
         <v>0.4666666666666666</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L57" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M57" t="n">
         <v>0.6533333333333333</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N57" t="n">
         <v>0.35694066507727</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O57" t="n">
         <v>6.016655557078</v>
       </c>
     </row>
